--- a/output/yearly_population_iteration_69_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_69_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6263</v>
+        <v>6773</v>
       </c>
       <c r="C2" t="n">
-        <v>3447</v>
+        <v>11630</v>
       </c>
       <c r="D2" t="n">
-        <v>30610</v>
+        <v>30073</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3644</v>
+        <v>3601</v>
       </c>
       <c r="C3" t="n">
-        <v>4265</v>
+        <v>3883</v>
       </c>
       <c r="D3" t="n">
-        <v>15840</v>
+        <v>14932</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2774</v>
+        <v>2935</v>
       </c>
       <c r="C4" t="n">
-        <v>5975</v>
+        <v>4608</v>
       </c>
       <c r="D4" t="n">
-        <v>8030</v>
+        <v>8182</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1870</v>
+        <v>1772</v>
       </c>
       <c r="C5" t="n">
-        <v>5787</v>
+        <v>3831</v>
       </c>
       <c r="D5" t="n">
-        <v>3000</v>
+        <v>3303</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1070</v>
+        <v>999</v>
       </c>
       <c r="C6" t="n">
-        <v>4200</v>
+        <v>2991</v>
       </c>
       <c r="D6" t="n">
-        <v>1161</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>498</v>
+        <v>483</v>
       </c>
       <c r="C7" t="n">
-        <v>2574</v>
+        <v>1932</v>
       </c>
       <c r="D7" t="n">
-        <v>643</v>
+        <v>682</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C8" t="n">
-        <v>1267</v>
+        <v>930</v>
       </c>
       <c r="D8" t="n">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>481</v>
+        <v>393</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7739</v>
+        <v>8502</v>
       </c>
       <c r="C2" t="n">
-        <v>10215</v>
+        <v>11992</v>
       </c>
       <c r="D2" t="n">
-        <v>26667</v>
+        <v>27959</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3847</v>
+        <v>4031</v>
       </c>
       <c r="C3" t="n">
-        <v>3507</v>
+        <v>6553</v>
       </c>
       <c r="D3" t="n">
-        <v>16691</v>
+        <v>15987</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2699</v>
+        <v>2758</v>
       </c>
       <c r="C4" t="n">
-        <v>5038</v>
+        <v>4126</v>
       </c>
       <c r="D4" t="n">
-        <v>8985</v>
+        <v>9034</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1980</v>
+        <v>1999</v>
       </c>
       <c r="C5" t="n">
-        <v>5692</v>
+        <v>4072</v>
       </c>
       <c r="D5" t="n">
-        <v>3604</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1264</v>
+        <v>1220</v>
       </c>
       <c r="C6" t="n">
-        <v>4831</v>
+        <v>3340</v>
       </c>
       <c r="D6" t="n">
-        <v>1410</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>649</v>
+        <v>627</v>
       </c>
       <c r="C7" t="n">
-        <v>3217</v>
+        <v>2379</v>
       </c>
       <c r="D7" t="n">
-        <v>701</v>
+        <v>760</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C8" t="n">
-        <v>1779</v>
+        <v>1361</v>
       </c>
       <c r="D8" t="n">
-        <v>448</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -1192,10 +1192,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>788</v>
+        <v>610</v>
       </c>
       <c r="D9" t="n">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>319</v>
+        <v>286</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1307,7 +1307,7 @@
         <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7221</v>
+        <v>8699</v>
       </c>
       <c r="C2" t="n">
-        <v>11487</v>
+        <v>9154</v>
       </c>
       <c r="D2" t="n">
-        <v>31787</v>
+        <v>38229</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4297</v>
+        <v>4713</v>
       </c>
       <c r="C3" t="n">
-        <v>5384</v>
+        <v>7777</v>
       </c>
       <c r="D3" t="n">
-        <v>16766</v>
+        <v>16400</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2664</v>
+        <v>2808</v>
       </c>
       <c r="C4" t="n">
-        <v>4267</v>
+        <v>5049</v>
       </c>
       <c r="D4" t="n">
-        <v>9661</v>
+        <v>9673</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2007</v>
+        <v>2046</v>
       </c>
       <c r="C5" t="n">
-        <v>5261</v>
+        <v>4010</v>
       </c>
       <c r="D5" t="n">
-        <v>4183</v>
+        <v>4537</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1397</v>
+        <v>1390</v>
       </c>
       <c r="C6" t="n">
-        <v>5121</v>
+        <v>3573</v>
       </c>
       <c r="D6" t="n">
-        <v>1686</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>787</v>
+        <v>771</v>
       </c>
       <c r="C7" t="n">
-        <v>3785</v>
+        <v>2740</v>
       </c>
       <c r="D7" t="n">
-        <v>777</v>
+        <v>866</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C8" t="n">
-        <v>2282</v>
+        <v>1759</v>
       </c>
       <c r="D8" t="n">
-        <v>475</v>
+        <v>489</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C9" t="n">
-        <v>1129</v>
+        <v>883</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>479</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1556,10 +1556,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>126</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1618,7 +1618,7 @@
         <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6809</v>
+        <v>8012</v>
       </c>
       <c r="C2" t="n">
-        <v>8086</v>
+        <v>6297</v>
       </c>
       <c r="D2" t="n">
-        <v>26395</v>
+        <v>31370</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4905</v>
+        <v>5363</v>
       </c>
       <c r="C3" t="n">
-        <v>8155</v>
+        <v>10575</v>
       </c>
       <c r="D3" t="n">
-        <v>18190</v>
+        <v>17928</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1854</v>
+        <v>1890</v>
       </c>
       <c r="C4" t="n">
-        <v>7262</v>
+        <v>6612</v>
       </c>
       <c r="D4" t="n">
-        <v>9145</v>
+        <v>9450</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1290</v>
+        <v>1284</v>
       </c>
       <c r="C5" t="n">
-        <v>5018</v>
+        <v>3501</v>
       </c>
       <c r="D5" t="n">
-        <v>2736</v>
+        <v>3053</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>727</v>
+        <v>712</v>
       </c>
       <c r="C6" t="n">
-        <v>3709</v>
+        <v>2685</v>
       </c>
       <c r="D6" t="n">
-        <v>761</v>
+        <v>848</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C7" t="n">
-        <v>2236</v>
+        <v>1723</v>
       </c>
       <c r="D7" t="n">
-        <v>465</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>1106</v>
+        <v>865</v>
       </c>
       <c r="D8" t="n">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>469</v>
+        <v>392</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1853,10 +1853,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
         <v>123</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1915,7 +1915,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4364</v>
+        <v>4902</v>
       </c>
       <c r="C2" t="n">
-        <v>4121</v>
+        <v>3379</v>
       </c>
       <c r="D2" t="n">
-        <v>19412</v>
+        <v>21801</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4911</v>
+        <v>5579</v>
       </c>
       <c r="C3" t="n">
-        <v>7397</v>
+        <v>7848</v>
       </c>
       <c r="D3" t="n">
-        <v>18221</v>
+        <v>18895</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2553</v>
+        <v>2761</v>
       </c>
       <c r="C4" t="n">
-        <v>7714</v>
+        <v>8554</v>
       </c>
       <c r="D4" t="n">
-        <v>10345</v>
+        <v>10474</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1412</v>
+        <v>1434</v>
       </c>
       <c r="C5" t="n">
-        <v>6037</v>
+        <v>4816</v>
       </c>
       <c r="D5" t="n">
-        <v>3443</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="C6" t="n">
-        <v>4363</v>
+        <v>3130</v>
       </c>
       <c r="D6" t="n">
-        <v>944</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C7" t="n">
-        <v>2771</v>
+        <v>2111</v>
       </c>
       <c r="D7" t="n">
-        <v>508</v>
+        <v>531</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>1443</v>
+        <v>1140</v>
       </c>
       <c r="D8" t="n">
-        <v>322</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>493</v>
+        <v>437</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
@@ -2212,7 +2212,7 @@
         <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4876</v>
+        <v>4688</v>
       </c>
       <c r="C2" t="n">
-        <v>10276</v>
+        <v>8855</v>
       </c>
       <c r="D2" t="n">
-        <v>15187</v>
+        <v>19882</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3941</v>
+        <v>4451</v>
       </c>
       <c r="C3" t="n">
-        <v>5269</v>
+        <v>5070</v>
       </c>
       <c r="D3" t="n">
-        <v>17333</v>
+        <v>18020</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3044</v>
+        <v>3383</v>
       </c>
       <c r="C4" t="n">
-        <v>7404</v>
+        <v>8030</v>
       </c>
       <c r="D4" t="n">
-        <v>11140</v>
+        <v>11529</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1665</v>
+        <v>1765</v>
       </c>
       <c r="C5" t="n">
-        <v>6668</v>
+        <v>6520</v>
       </c>
       <c r="D5" t="n">
-        <v>4398</v>
+        <v>4723</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>988</v>
+        <v>1009</v>
       </c>
       <c r="C6" t="n">
-        <v>5087</v>
+        <v>3844</v>
       </c>
       <c r="D6" t="n">
-        <v>1291</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C7" t="n">
-        <v>3452</v>
+        <v>2570</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C8" t="n">
-        <v>1964</v>
+        <v>1540</v>
       </c>
       <c r="D8" t="n">
-        <v>345</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>832</v>
+        <v>702</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
         <v>23</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2950</v>
+        <v>2786</v>
       </c>
       <c r="C2" t="n">
-        <v>4971</v>
+        <v>4140</v>
       </c>
       <c r="D2" t="n">
-        <v>10617</v>
+        <v>13863</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4008</v>
+        <v>4386</v>
       </c>
       <c r="C3" t="n">
-        <v>6727</v>
+        <v>6187</v>
       </c>
       <c r="D3" t="n">
-        <v>16721</v>
+        <v>17810</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3334</v>
+        <v>3701</v>
       </c>
       <c r="C4" t="n">
-        <v>7304</v>
+        <v>7667</v>
       </c>
       <c r="D4" t="n">
-        <v>11955</v>
+        <v>12338</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1729</v>
+        <v>1826</v>
       </c>
       <c r="C5" t="n">
-        <v>7915</v>
+        <v>7868</v>
       </c>
       <c r="D5" t="n">
-        <v>4610</v>
+        <v>4977</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>800</v>
+        <v>827</v>
       </c>
       <c r="C6" t="n">
-        <v>6042</v>
+        <v>4685</v>
       </c>
       <c r="D6" t="n">
-        <v>1251</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>3599</v>
+        <v>2728</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1373</v>
+        <v>1155</v>
       </c>
       <c r="D8" t="n">
-        <v>367</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
         <v>22</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3236</v>
+        <v>4426</v>
       </c>
       <c r="C2" t="n">
-        <v>9351</v>
+        <v>3949</v>
       </c>
       <c r="D2" t="n">
-        <v>16998</v>
+        <v>12353</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3061</v>
+        <v>3193</v>
       </c>
       <c r="C3" t="n">
-        <v>5266</v>
+        <v>4685</v>
       </c>
       <c r="D3" t="n">
-        <v>14842</v>
+        <v>16247</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3172</v>
+        <v>3506</v>
       </c>
       <c r="C4" t="n">
-        <v>6956</v>
+        <v>6884</v>
       </c>
       <c r="D4" t="n">
-        <v>12323</v>
+        <v>12803</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2084</v>
+        <v>2267</v>
       </c>
       <c r="C5" t="n">
-        <v>7562</v>
+        <v>7691</v>
       </c>
       <c r="D5" t="n">
-        <v>5527</v>
+        <v>5885</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1026</v>
+        <v>1080</v>
       </c>
       <c r="C6" t="n">
-        <v>6803</v>
+        <v>6002</v>
       </c>
       <c r="D6" t="n">
-        <v>1698</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="C7" t="n">
-        <v>4601</v>
+        <v>3520</v>
       </c>
       <c r="D7" t="n">
-        <v>636</v>
+        <v>697</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>2162</v>
+        <v>1758</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>641</v>
+        <v>572</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2257</v>
+        <v>3030</v>
       </c>
       <c r="C2" t="n">
-        <v>5550</v>
+        <v>2344</v>
       </c>
       <c r="D2" t="n">
-        <v>12756</v>
+        <v>9952</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2731</v>
+        <v>3143</v>
       </c>
       <c r="C3" t="n">
-        <v>6249</v>
+        <v>3998</v>
       </c>
       <c r="D3" t="n">
-        <v>14299</v>
+        <v>14895</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2891</v>
+        <v>3146</v>
       </c>
       <c r="C4" t="n">
-        <v>6295</v>
+        <v>6052</v>
       </c>
       <c r="D4" t="n">
-        <v>12381</v>
+        <v>13122</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2281</v>
+        <v>2479</v>
       </c>
       <c r="C5" t="n">
-        <v>7485</v>
+        <v>7465</v>
       </c>
       <c r="D5" t="n">
-        <v>6182</v>
+        <v>6493</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1184</v>
+        <v>1293</v>
       </c>
       <c r="C6" t="n">
-        <v>7311</v>
+        <v>6832</v>
       </c>
       <c r="D6" t="n">
-        <v>2005</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="C7" t="n">
-        <v>5411</v>
+        <v>4309</v>
       </c>
       <c r="D7" t="n">
-        <v>711</v>
+        <v>779</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>2724</v>
+        <v>2233</v>
       </c>
       <c r="D8" t="n">
-        <v>402</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>703</v>
+        <v>649</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3036</v>
+        <v>4484</v>
       </c>
       <c r="C2" t="n">
-        <v>15875</v>
+        <v>2902</v>
       </c>
       <c r="D2" t="n">
-        <v>12440</v>
+        <v>10131</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2167</v>
+        <v>2610</v>
       </c>
       <c r="C3" t="n">
-        <v>5388</v>
+        <v>2974</v>
       </c>
       <c r="D3" t="n">
-        <v>13335</v>
+        <v>13348</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2466</v>
+        <v>2759</v>
       </c>
       <c r="C4" t="n">
-        <v>6145</v>
+        <v>5058</v>
       </c>
       <c r="D4" t="n">
-        <v>12143</v>
+        <v>12978</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2263</v>
+        <v>2465</v>
       </c>
       <c r="C5" t="n">
-        <v>6872</v>
+        <v>6740</v>
       </c>
       <c r="D5" t="n">
-        <v>6827</v>
+        <v>7186</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1430</v>
+        <v>1570</v>
       </c>
       <c r="C6" t="n">
-        <v>7315</v>
+        <v>7017</v>
       </c>
       <c r="D6" t="n">
-        <v>2500</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>480</v>
+        <v>529</v>
       </c>
       <c r="C7" t="n">
-        <v>6079</v>
+        <v>5289</v>
       </c>
       <c r="D7" t="n">
-        <v>855</v>
+        <v>944</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>3618</v>
+        <v>2944</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1343</v>
+        <v>1167</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="D10" t="n">
         <v>186</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>38</v>
+      </c>
+      <c r="D14" t="n">
         <v>37</v>
-      </c>
-      <c r="D14" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6624</v>
+        <v>4954</v>
       </c>
       <c r="C2" t="n">
-        <v>14619</v>
+        <v>8077</v>
       </c>
       <c r="D2" t="n">
-        <v>6108</v>
+        <v>13743</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2220</v>
+        <v>3206</v>
       </c>
       <c r="C2" t="n">
-        <v>9272</v>
+        <v>1671</v>
       </c>
       <c r="D2" t="n">
-        <v>9255</v>
+        <v>7457</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2884</v>
+        <v>3511</v>
       </c>
       <c r="C3" t="n">
-        <v>8194</v>
+        <v>3219</v>
       </c>
       <c r="D3" t="n">
-        <v>14430</v>
+        <v>14334</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3351</v>
+        <v>3666</v>
       </c>
       <c r="C4" t="n">
-        <v>8548</v>
+        <v>7276</v>
       </c>
       <c r="D4" t="n">
-        <v>12363</v>
+        <v>13311</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1342</v>
+        <v>1519</v>
       </c>
       <c r="C5" t="n">
-        <v>10232</v>
+        <v>9836</v>
       </c>
       <c r="D5" t="n">
-        <v>6164</v>
+        <v>6523</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>443</v>
+        <v>488</v>
       </c>
       <c r="C6" t="n">
-        <v>7247</v>
+        <v>6558</v>
       </c>
       <c r="D6" t="n">
-        <v>1929</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>3545</v>
+        <v>2885</v>
       </c>
       <c r="D7" t="n">
-        <v>531</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1316</v>
+        <v>1143</v>
       </c>
       <c r="D8" t="n">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="D9" t="n">
         <v>182</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="D10" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>37</v>
+      </c>
+      <c r="D13" t="n">
         <v>36</v>
-      </c>
-      <c r="D13" t="n">
-        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7468</v>
+        <v>7817</v>
       </c>
       <c r="C2" t="n">
-        <v>7245</v>
+        <v>7175</v>
       </c>
       <c r="D2" t="n">
-        <v>19274</v>
+        <v>24993</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2814</v>
+        <v>2106</v>
       </c>
       <c r="C3" t="n">
-        <v>7367</v>
+        <v>4070</v>
       </c>
       <c r="D3" t="n">
-        <v>1665</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="4">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5670</v>
+        <v>4994</v>
       </c>
       <c r="C2" t="n">
-        <v>8735</v>
+        <v>5662</v>
       </c>
       <c r="D2" t="n">
-        <v>36141</v>
+        <v>27108</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4221</v>
+        <v>4068</v>
       </c>
       <c r="C3" t="n">
-        <v>6293</v>
+        <v>5025</v>
       </c>
       <c r="D3" t="n">
-        <v>4500</v>
+        <v>6434</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1257</v>
+        <v>949</v>
       </c>
       <c r="C4" t="n">
-        <v>4360</v>
+        <v>2429</v>
       </c>
       <c r="D4" t="n">
-        <v>1516</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="5">
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4927,7 +4927,7 @@
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>77</v>
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>4455</v>
       </c>
       <c r="C2" t="n">
-        <v>7910</v>
+        <v>6618</v>
       </c>
       <c r="D2" t="n">
-        <v>26829</v>
+        <v>26852</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4047</v>
+        <v>3725</v>
       </c>
       <c r="C3" t="n">
-        <v>6590</v>
+        <v>4653</v>
       </c>
       <c r="D3" t="n">
-        <v>9238</v>
+        <v>9278</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2304</v>
+        <v>2126</v>
       </c>
       <c r="C4" t="n">
-        <v>5345</v>
+        <v>3800</v>
       </c>
       <c r="D4" t="n">
-        <v>2042</v>
+        <v>2615</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>556</v>
+        <v>442</v>
       </c>
       <c r="C5" t="n">
-        <v>2442</v>
+        <v>1425</v>
       </c>
       <c r="D5" t="n">
-        <v>1219</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5322,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5361,7 +5361,7 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5403,7 +5403,7 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6672</v>
+        <v>5164</v>
       </c>
       <c r="C2" t="n">
-        <v>11539</v>
+        <v>5459</v>
       </c>
       <c r="D2" t="n">
-        <v>28754</v>
+        <v>26536</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3765</v>
+        <v>3353</v>
       </c>
       <c r="C3" t="n">
-        <v>6327</v>
+        <v>4922</v>
       </c>
       <c r="D3" t="n">
-        <v>11135</v>
+        <v>11296</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2650</v>
+        <v>2456</v>
       </c>
       <c r="C4" t="n">
-        <v>5827</v>
+        <v>4134</v>
       </c>
       <c r="D4" t="n">
-        <v>3203</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1161</v>
+        <v>1047</v>
       </c>
       <c r="C5" t="n">
-        <v>3868</v>
+        <v>2626</v>
       </c>
       <c r="D5" t="n">
-        <v>1324</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>297</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>1349</v>
+        <v>860</v>
       </c>
       <c r="D6" t="n">
-        <v>928</v>
+        <v>955</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
         <v>149</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5714,7 +5714,7 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6502</v>
+        <v>7115</v>
       </c>
       <c r="C2" t="n">
-        <v>9302</v>
+        <v>6700</v>
       </c>
       <c r="D2" t="n">
-        <v>32065</v>
+        <v>28978</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3703</v>
+        <v>3077</v>
       </c>
       <c r="C3" t="n">
-        <v>7290</v>
+        <v>4255</v>
       </c>
       <c r="D3" t="n">
-        <v>12129</v>
+        <v>12059</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1956</v>
+        <v>1806</v>
       </c>
       <c r="C4" t="n">
-        <v>4978</v>
+        <v>3700</v>
       </c>
       <c r="D4" t="n">
-        <v>3875</v>
+        <v>4373</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>975</v>
+        <v>902</v>
       </c>
       <c r="C5" t="n">
-        <v>3502</v>
+        <v>2487</v>
       </c>
       <c r="D5" t="n">
-        <v>1302</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>338</v>
+        <v>305</v>
       </c>
       <c r="C6" t="n">
-        <v>1729</v>
+        <v>1161</v>
       </c>
       <c r="D6" t="n">
-        <v>747</v>
+        <v>789</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C7" t="n">
-        <v>520</v>
+        <v>383</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>78</v>
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5032</v>
+        <v>6081</v>
       </c>
       <c r="C2" t="n">
-        <v>5822</v>
+        <v>6570</v>
       </c>
       <c r="D2" t="n">
-        <v>26617</v>
+        <v>24879</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4198</v>
+        <v>4218</v>
       </c>
       <c r="C3" t="n">
-        <v>7268</v>
+        <v>4888</v>
       </c>
       <c r="D3" t="n">
-        <v>14585</v>
+        <v>14013</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2458</v>
+        <v>2117</v>
       </c>
       <c r="C4" t="n">
-        <v>6228</v>
+        <v>3958</v>
       </c>
       <c r="D4" t="n">
-        <v>5421</v>
+        <v>5747</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1294</v>
+        <v>1209</v>
       </c>
       <c r="C5" t="n">
-        <v>4265</v>
+        <v>3145</v>
       </c>
       <c r="D5" t="n">
-        <v>1756</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>592</v>
+        <v>557</v>
       </c>
       <c r="C6" t="n">
-        <v>2678</v>
+        <v>1897</v>
       </c>
       <c r="D6" t="n">
-        <v>830</v>
+        <v>903</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="C7" t="n">
-        <v>1166</v>
+        <v>817</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6308,10 +6308,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5104</v>
+        <v>4517</v>
       </c>
       <c r="C2" t="n">
-        <v>3908</v>
+        <v>3859</v>
       </c>
       <c r="D2" t="n">
-        <v>26327</v>
+        <v>23105</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3823</v>
+        <v>4216</v>
       </c>
       <c r="C3" t="n">
-        <v>5678</v>
+        <v>5019</v>
       </c>
       <c r="D3" t="n">
-        <v>15387</v>
+        <v>14742</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2797</v>
+        <v>2716</v>
       </c>
       <c r="C4" t="n">
-        <v>6657</v>
+        <v>4355</v>
       </c>
       <c r="D4" t="n">
-        <v>6927</v>
+        <v>7159</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1611</v>
+        <v>1450</v>
       </c>
       <c r="C5" t="n">
-        <v>5193</v>
+        <v>3524</v>
       </c>
       <c r="D5" t="n">
-        <v>2319</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>843</v>
+        <v>802</v>
       </c>
       <c r="C6" t="n">
-        <v>3415</v>
+        <v>2534</v>
       </c>
       <c r="D6" t="n">
-        <v>978</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>334</v>
+        <v>318</v>
       </c>
       <c r="C7" t="n">
-        <v>1921</v>
+        <v>1377</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>753</v>
+        <v>559</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>288</v>
+        <v>257</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6493,7 +6493,7 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
         <v>238</v>
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>121</v>
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +6619,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>

--- a/output/yearly_population_iteration_69_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_69_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6773</v>
+        <v>6029</v>
       </c>
       <c r="C2" t="n">
-        <v>11630</v>
+        <v>5381</v>
       </c>
       <c r="D2" t="n">
-        <v>30073</v>
+        <v>19265</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3601</v>
+        <v>3734</v>
       </c>
       <c r="C3" t="n">
-        <v>3883</v>
+        <v>4360</v>
       </c>
       <c r="D3" t="n">
-        <v>14932</v>
+        <v>10998</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2935</v>
+        <v>2923</v>
       </c>
       <c r="C4" t="n">
-        <v>4608</v>
+        <v>4375</v>
       </c>
       <c r="D4" t="n">
-        <v>8182</v>
+        <v>5308</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1772</v>
+        <v>1932</v>
       </c>
       <c r="C5" t="n">
-        <v>3831</v>
+        <v>3829</v>
       </c>
       <c r="D5" t="n">
-        <v>3303</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>999</v>
+        <v>1132</v>
       </c>
       <c r="C6" t="n">
-        <v>2991</v>
+        <v>2599</v>
       </c>
       <c r="D6" t="n">
-        <v>1308</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>483</v>
+        <v>547</v>
       </c>
       <c r="C7" t="n">
-        <v>1932</v>
+        <v>1698</v>
       </c>
       <c r="D7" t="n">
-        <v>682</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>174</v>
+        <v>213</v>
       </c>
       <c r="C8" t="n">
-        <v>930</v>
+        <v>850</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1052,7 +1052,7 @@
         <v>99</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8502</v>
+        <v>9720</v>
       </c>
       <c r="C2" t="n">
-        <v>11992</v>
+        <v>15284</v>
       </c>
       <c r="D2" t="n">
-        <v>27959</v>
+        <v>21431</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4031</v>
+        <v>3887</v>
       </c>
       <c r="C3" t="n">
-        <v>6553</v>
+        <v>4247</v>
       </c>
       <c r="D3" t="n">
-        <v>15987</v>
+        <v>11431</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2758</v>
+        <v>2812</v>
       </c>
       <c r="C4" t="n">
-        <v>4126</v>
+        <v>4276</v>
       </c>
       <c r="D4" t="n">
-        <v>9034</v>
+        <v>6129</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1999</v>
+        <v>2099</v>
       </c>
       <c r="C5" t="n">
-        <v>4072</v>
+        <v>3974</v>
       </c>
       <c r="D5" t="n">
-        <v>3920</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1220</v>
+        <v>1369</v>
       </c>
       <c r="C6" t="n">
-        <v>3340</v>
+        <v>3151</v>
       </c>
       <c r="D6" t="n">
-        <v>1596</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>627</v>
+        <v>721</v>
       </c>
       <c r="C7" t="n">
-        <v>2379</v>
+        <v>2095</v>
       </c>
       <c r="D7" t="n">
-        <v>760</v>
+        <v>693</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>265</v>
+        <v>318</v>
       </c>
       <c r="C8" t="n">
-        <v>1361</v>
+        <v>1231</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="C9" t="n">
-        <v>610</v>
+        <v>573</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8699</v>
+        <v>9053</v>
       </c>
       <c r="C2" t="n">
-        <v>9154</v>
+        <v>11692</v>
       </c>
       <c r="D2" t="n">
-        <v>38229</v>
+        <v>36396</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4713</v>
+        <v>5097</v>
       </c>
       <c r="C3" t="n">
-        <v>7777</v>
+        <v>7989</v>
       </c>
       <c r="D3" t="n">
-        <v>16400</v>
+        <v>11961</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2808</v>
+        <v>2810</v>
       </c>
       <c r="C4" t="n">
-        <v>5049</v>
+        <v>4173</v>
       </c>
       <c r="D4" t="n">
-        <v>9673</v>
+        <v>6698</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2046</v>
+        <v>2132</v>
       </c>
       <c r="C5" t="n">
-        <v>4010</v>
+        <v>3986</v>
       </c>
       <c r="D5" t="n">
-        <v>4537</v>
+        <v>3011</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1390</v>
+        <v>1527</v>
       </c>
       <c r="C6" t="n">
-        <v>3573</v>
+        <v>3476</v>
       </c>
       <c r="D6" t="n">
-        <v>1871</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>771</v>
+        <v>888</v>
       </c>
       <c r="C7" t="n">
-        <v>2740</v>
+        <v>2518</v>
       </c>
       <c r="D7" t="n">
-        <v>866</v>
+        <v>758</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>357</v>
+        <v>430</v>
       </c>
       <c r="C8" t="n">
-        <v>1759</v>
+        <v>1586</v>
       </c>
       <c r="D8" t="n">
-        <v>489</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="C9" t="n">
-        <v>883</v>
+        <v>825</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C10" t="n">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8012</v>
+        <v>8296</v>
       </c>
       <c r="C2" t="n">
-        <v>6297</v>
+        <v>7763</v>
       </c>
       <c r="D2" t="n">
-        <v>31370</v>
+        <v>29284</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5363</v>
+        <v>5694</v>
       </c>
       <c r="C3" t="n">
-        <v>10575</v>
+        <v>10902</v>
       </c>
       <c r="D3" t="n">
-        <v>17928</v>
+        <v>13307</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1890</v>
+        <v>1969</v>
       </c>
       <c r="C4" t="n">
-        <v>6612</v>
+        <v>6190</v>
       </c>
       <c r="D4" t="n">
-        <v>9450</v>
+        <v>6489</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1284</v>
+        <v>1410</v>
       </c>
       <c r="C5" t="n">
-        <v>3501</v>
+        <v>3406</v>
       </c>
       <c r="D5" t="n">
-        <v>3053</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>712</v>
+        <v>820</v>
       </c>
       <c r="C6" t="n">
-        <v>2685</v>
+        <v>2467</v>
       </c>
       <c r="D6" t="n">
-        <v>848</v>
+        <v>742</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>329</v>
+        <v>397</v>
       </c>
       <c r="C7" t="n">
-        <v>1723</v>
+        <v>1554</v>
       </c>
       <c r="D7" t="n">
-        <v>479</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="C8" t="n">
-        <v>865</v>
+        <v>808</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C9" t="n">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4902</v>
+        <v>4952</v>
       </c>
       <c r="C2" t="n">
-        <v>3379</v>
+        <v>3251</v>
       </c>
       <c r="D2" t="n">
-        <v>21801</v>
+        <v>19653</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5579</v>
+        <v>5874</v>
       </c>
       <c r="C3" t="n">
-        <v>7848</v>
+        <v>8524</v>
       </c>
       <c r="D3" t="n">
-        <v>18895</v>
+        <v>14947</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2761</v>
+        <v>2939</v>
       </c>
       <c r="C4" t="n">
-        <v>8554</v>
+        <v>8560</v>
       </c>
       <c r="D4" t="n">
-        <v>10474</v>
+        <v>7463</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1434</v>
+        <v>1543</v>
       </c>
       <c r="C5" t="n">
-        <v>4816</v>
+        <v>4674</v>
       </c>
       <c r="D5" t="n">
-        <v>3817</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>848</v>
+        <v>989</v>
       </c>
       <c r="C6" t="n">
-        <v>3130</v>
+        <v>2926</v>
       </c>
       <c r="D6" t="n">
-        <v>1074</v>
+        <v>891</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>308</v>
+        <v>377</v>
       </c>
       <c r="C7" t="n">
-        <v>2111</v>
+        <v>1949</v>
       </c>
       <c r="D7" t="n">
-        <v>531</v>
+        <v>510</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>1140</v>
+        <v>1048</v>
       </c>
       <c r="D8" t="n">
-        <v>333</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4688</v>
+        <v>4732</v>
       </c>
       <c r="C2" t="n">
-        <v>8855</v>
+        <v>5661</v>
       </c>
       <c r="D2" t="n">
-        <v>19882</v>
+        <v>18400</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4451</v>
+        <v>4595</v>
       </c>
       <c r="C3" t="n">
-        <v>5070</v>
+        <v>5224</v>
       </c>
       <c r="D3" t="n">
-        <v>18020</v>
+        <v>14596</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3383</v>
+        <v>3654</v>
       </c>
       <c r="C4" t="n">
-        <v>8030</v>
+        <v>8445</v>
       </c>
       <c r="D4" t="n">
-        <v>11529</v>
+        <v>8529</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1765</v>
+        <v>1899</v>
       </c>
       <c r="C5" t="n">
-        <v>6520</v>
+        <v>6442</v>
       </c>
       <c r="D5" t="n">
-        <v>4723</v>
+        <v>3379</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1009</v>
+        <v>1130</v>
       </c>
       <c r="C6" t="n">
-        <v>3844</v>
+        <v>3730</v>
       </c>
       <c r="D6" t="n">
-        <v>1454</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>452</v>
+        <v>554</v>
       </c>
       <c r="C7" t="n">
-        <v>2570</v>
+        <v>2379</v>
       </c>
       <c r="D7" t="n">
-        <v>600</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="C8" t="n">
-        <v>1540</v>
+        <v>1437</v>
       </c>
       <c r="D8" t="n">
-        <v>354</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>702</v>
+        <v>691</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2565,7 +2565,7 @@
         <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2786</v>
+        <v>2806</v>
       </c>
       <c r="C2" t="n">
-        <v>4140</v>
+        <v>2595</v>
       </c>
       <c r="D2" t="n">
-        <v>13863</v>
+        <v>12697</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4386</v>
+        <v>4463</v>
       </c>
       <c r="C3" t="n">
-        <v>6187</v>
+        <v>5157</v>
       </c>
       <c r="D3" t="n">
-        <v>17810</v>
+        <v>14671</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3701</v>
+        <v>4033</v>
       </c>
       <c r="C4" t="n">
-        <v>7667</v>
+        <v>8047</v>
       </c>
       <c r="D4" t="n">
-        <v>12338</v>
+        <v>9261</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1826</v>
+        <v>1995</v>
       </c>
       <c r="C5" t="n">
-        <v>7868</v>
+        <v>7762</v>
       </c>
       <c r="D5" t="n">
-        <v>4977</v>
+        <v>3684</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>827</v>
+        <v>981</v>
       </c>
       <c r="C6" t="n">
-        <v>4685</v>
+        <v>4664</v>
       </c>
       <c r="D6" t="n">
-        <v>1415</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="C7" t="n">
-        <v>2728</v>
+        <v>2566</v>
       </c>
       <c r="D7" t="n">
-        <v>593</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>1155</v>
+        <v>1127</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -2862,7 +2862,7 @@
         <v>64</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4426</v>
+        <v>3340</v>
       </c>
       <c r="C2" t="n">
-        <v>3949</v>
+        <v>3144</v>
       </c>
       <c r="D2" t="n">
-        <v>12353</v>
+        <v>11952</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3193</v>
+        <v>3224</v>
       </c>
       <c r="C3" t="n">
-        <v>4685</v>
+        <v>3505</v>
       </c>
       <c r="D3" t="n">
-        <v>16247</v>
+        <v>13416</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3506</v>
+        <v>3685</v>
       </c>
       <c r="C4" t="n">
-        <v>6884</v>
+        <v>6541</v>
       </c>
       <c r="D4" t="n">
-        <v>12803</v>
+        <v>9862</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2267</v>
+        <v>2506</v>
       </c>
       <c r="C5" t="n">
-        <v>7691</v>
+        <v>7806</v>
       </c>
       <c r="D5" t="n">
-        <v>5885</v>
+        <v>4428</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1080</v>
+        <v>1260</v>
       </c>
       <c r="C6" t="n">
-        <v>6002</v>
+        <v>6004</v>
       </c>
       <c r="D6" t="n">
-        <v>1875</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>312</v>
+        <v>382</v>
       </c>
       <c r="C7" t="n">
-        <v>3520</v>
+        <v>3478</v>
       </c>
       <c r="D7" t="n">
-        <v>697</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>1758</v>
+        <v>1684</v>
       </c>
       <c r="D8" t="n">
-        <v>399</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>572</v>
+        <v>588</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
         <v>134</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3030</v>
+        <v>2525</v>
       </c>
       <c r="C2" t="n">
-        <v>2344</v>
+        <v>2395</v>
       </c>
       <c r="D2" t="n">
-        <v>9952</v>
+        <v>8938</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3143</v>
+        <v>2857</v>
       </c>
       <c r="C3" t="n">
-        <v>3998</v>
+        <v>3041</v>
       </c>
       <c r="D3" t="n">
-        <v>14895</v>
+        <v>12510</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3146</v>
+        <v>3237</v>
       </c>
       <c r="C4" t="n">
-        <v>6052</v>
+        <v>5310</v>
       </c>
       <c r="D4" t="n">
-        <v>13122</v>
+        <v>10134</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2479</v>
+        <v>2744</v>
       </c>
       <c r="C5" t="n">
-        <v>7465</v>
+        <v>7469</v>
       </c>
       <c r="D5" t="n">
-        <v>6493</v>
+        <v>5004</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1293</v>
+        <v>1501</v>
       </c>
       <c r="C6" t="n">
-        <v>6832</v>
+        <v>6827</v>
       </c>
       <c r="D6" t="n">
-        <v>2254</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>281</v>
+        <v>359</v>
       </c>
       <c r="C7" t="n">
-        <v>4309</v>
+        <v>4358</v>
       </c>
       <c r="D7" t="n">
-        <v>779</v>
+        <v>710</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>2233</v>
+        <v>2153</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>649</v>
+        <v>699</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4484</v>
+        <v>4918</v>
       </c>
       <c r="C2" t="n">
-        <v>2902</v>
+        <v>9690</v>
       </c>
       <c r="D2" t="n">
-        <v>10131</v>
+        <v>11781</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2610</v>
+        <v>2301</v>
       </c>
       <c r="C3" t="n">
-        <v>2974</v>
+        <v>2487</v>
       </c>
       <c r="D3" t="n">
-        <v>13348</v>
+        <v>11352</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2759</v>
+        <v>2693</v>
       </c>
       <c r="C4" t="n">
-        <v>5058</v>
+        <v>4168</v>
       </c>
       <c r="D4" t="n">
-        <v>12978</v>
+        <v>10070</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2465</v>
+        <v>2689</v>
       </c>
       <c r="C5" t="n">
-        <v>6740</v>
+        <v>6473</v>
       </c>
       <c r="D5" t="n">
-        <v>7186</v>
+        <v>5590</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1570</v>
+        <v>1796</v>
       </c>
       <c r="C6" t="n">
-        <v>7017</v>
+        <v>7020</v>
       </c>
       <c r="D6" t="n">
-        <v>2754</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>529</v>
+        <v>647</v>
       </c>
       <c r="C7" t="n">
-        <v>5289</v>
+        <v>5299</v>
       </c>
       <c r="D7" t="n">
-        <v>944</v>
+        <v>838</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>2944</v>
+        <v>2972</v>
       </c>
       <c r="D8" t="n">
-        <v>446</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>1167</v>
+        <v>1183</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>352</v>
+        <v>385</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
         <v>138</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4954</v>
+        <v>6724</v>
       </c>
       <c r="C2" t="n">
-        <v>8077</v>
+        <v>5972</v>
       </c>
       <c r="D2" t="n">
-        <v>13743</v>
+        <v>7478</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3206</v>
+        <v>3480</v>
       </c>
       <c r="C2" t="n">
-        <v>1671</v>
+        <v>5426</v>
       </c>
       <c r="D2" t="n">
-        <v>7457</v>
+        <v>8670</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3511</v>
+        <v>3281</v>
       </c>
       <c r="C3" t="n">
-        <v>3219</v>
+        <v>4426</v>
       </c>
       <c r="D3" t="n">
-        <v>14334</v>
+        <v>12328</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3666</v>
+        <v>3830</v>
       </c>
       <c r="C4" t="n">
-        <v>7276</v>
+        <v>6214</v>
       </c>
       <c r="D4" t="n">
-        <v>13311</v>
+        <v>10278</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1519</v>
+        <v>1758</v>
       </c>
       <c r="C5" t="n">
-        <v>9836</v>
+        <v>9722</v>
       </c>
       <c r="D5" t="n">
-        <v>6523</v>
+        <v>5148</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>488</v>
+        <v>597</v>
       </c>
       <c r="C6" t="n">
-        <v>6558</v>
+        <v>6637</v>
       </c>
       <c r="D6" t="n">
-        <v>2154</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="C7" t="n">
-        <v>2885</v>
+        <v>2912</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>1143</v>
+        <v>1159</v>
       </c>
       <c r="D8" t="n">
-        <v>293</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>344</v>
+        <v>377</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
         <v>135</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7817</v>
+        <v>7517</v>
       </c>
       <c r="C2" t="n">
-        <v>7175</v>
+        <v>6736</v>
       </c>
       <c r="D2" t="n">
-        <v>24993</v>
+        <v>9378</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2106</v>
+        <v>2856</v>
       </c>
       <c r="C3" t="n">
-        <v>4070</v>
+        <v>3009</v>
       </c>
       <c r="D3" t="n">
-        <v>2948</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>4753</v>
+      </c>
+      <c r="C2" t="n">
         <v>4994</v>
       </c>
-      <c r="C2" t="n">
-        <v>5662</v>
-      </c>
       <c r="D2" t="n">
-        <v>27108</v>
+        <v>16829</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4068</v>
+        <v>4259</v>
       </c>
       <c r="C3" t="n">
-        <v>5025</v>
+        <v>4438</v>
       </c>
       <c r="D3" t="n">
-        <v>6434</v>
+        <v>3012</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>949</v>
+        <v>1274</v>
       </c>
       <c r="C4" t="n">
-        <v>2429</v>
+        <v>1834</v>
       </c>
       <c r="D4" t="n">
-        <v>1775</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4455</v>
+        <v>5070</v>
       </c>
       <c r="C2" t="n">
-        <v>6618</v>
+        <v>4312</v>
       </c>
       <c r="D2" t="n">
-        <v>26852</v>
+        <v>13848</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3725</v>
+        <v>3713</v>
       </c>
       <c r="C3" t="n">
-        <v>4653</v>
+        <v>4103</v>
       </c>
       <c r="D3" t="n">
-        <v>9278</v>
+        <v>5005</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2126</v>
+        <v>2342</v>
       </c>
       <c r="C4" t="n">
-        <v>3800</v>
+        <v>3270</v>
       </c>
       <c r="D4" t="n">
-        <v>2615</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>442</v>
+        <v>583</v>
       </c>
       <c r="C5" t="n">
-        <v>1425</v>
+        <v>1096</v>
       </c>
       <c r="D5" t="n">
-        <v>1255</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
         <v>210</v>
@@ -5260,7 +5260,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
         <v>177</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5164</v>
+        <v>5876</v>
       </c>
       <c r="C2" t="n">
-        <v>5459</v>
+        <v>5900</v>
       </c>
       <c r="D2" t="n">
-        <v>26536</v>
+        <v>15224</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3353</v>
+        <v>3582</v>
       </c>
       <c r="C3" t="n">
-        <v>4922</v>
+        <v>3659</v>
       </c>
       <c r="D3" t="n">
-        <v>11296</v>
+        <v>5996</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2456</v>
+        <v>2564</v>
       </c>
       <c r="C4" t="n">
-        <v>4134</v>
+        <v>3657</v>
       </c>
       <c r="D4" t="n">
-        <v>3750</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1047</v>
+        <v>1219</v>
       </c>
       <c r="C5" t="n">
-        <v>2626</v>
+        <v>2221</v>
       </c>
       <c r="D5" t="n">
-        <v>1439</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>314</v>
       </c>
       <c r="C6" t="n">
-        <v>860</v>
+        <v>703</v>
       </c>
       <c r="D6" t="n">
-        <v>955</v>
+        <v>948</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5633,7 +5633,7 @@
         <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7115</v>
+        <v>6770</v>
       </c>
       <c r="C2" t="n">
-        <v>6700</v>
+        <v>8689</v>
       </c>
       <c r="D2" t="n">
-        <v>28978</v>
+        <v>25177</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3077</v>
+        <v>3432</v>
       </c>
       <c r="C3" t="n">
-        <v>4255</v>
+        <v>3951</v>
       </c>
       <c r="D3" t="n">
-        <v>12059</v>
+        <v>6563</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1806</v>
+        <v>1920</v>
       </c>
       <c r="C4" t="n">
-        <v>3700</v>
+        <v>3000</v>
       </c>
       <c r="D4" t="n">
-        <v>4373</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>902</v>
+        <v>989</v>
       </c>
       <c r="C5" t="n">
-        <v>2487</v>
+        <v>2162</v>
       </c>
       <c r="D5" t="n">
-        <v>1442</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>305</v>
+        <v>364</v>
       </c>
       <c r="C6" t="n">
-        <v>1161</v>
+        <v>999</v>
       </c>
       <c r="D6" t="n">
-        <v>789</v>
+        <v>757</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="C7" t="n">
-        <v>383</v>
+        <v>337</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D9" t="n">
         <v>270</v>
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6081</v>
+        <v>5382</v>
       </c>
       <c r="C2" t="n">
-        <v>6570</v>
+        <v>4225</v>
       </c>
       <c r="D2" t="n">
-        <v>24879</v>
+        <v>20417</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4218</v>
+        <v>4269</v>
       </c>
       <c r="C3" t="n">
-        <v>4888</v>
+        <v>5814</v>
       </c>
       <c r="D3" t="n">
-        <v>14013</v>
+        <v>9345</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2117</v>
+        <v>2364</v>
       </c>
       <c r="C4" t="n">
-        <v>3958</v>
+        <v>3493</v>
       </c>
       <c r="D4" t="n">
-        <v>5747</v>
+        <v>3295</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1209</v>
+        <v>1307</v>
       </c>
       <c r="C5" t="n">
-        <v>3145</v>
+        <v>2623</v>
       </c>
       <c r="D5" t="n">
-        <v>1989</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>557</v>
+        <v>628</v>
       </c>
       <c r="C6" t="n">
-        <v>1897</v>
+        <v>1667</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>815</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>175</v>
+        <v>214</v>
       </c>
       <c r="C7" t="n">
-        <v>817</v>
+        <v>719</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="D8" t="n">
         <v>385</v>
@@ -6168,10 +6168,10 @@
         <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,10 +6238,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6294,7 +6294,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6339,7 +6339,7 @@
         <v>84</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4517</v>
+        <v>5162</v>
       </c>
       <c r="C2" t="n">
-        <v>3859</v>
+        <v>5717</v>
       </c>
       <c r="D2" t="n">
-        <v>23105</v>
+        <v>18934</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4216</v>
+        <v>3971</v>
       </c>
       <c r="C3" t="n">
-        <v>5019</v>
+        <v>4260</v>
       </c>
       <c r="D3" t="n">
-        <v>14742</v>
+        <v>10443</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2716</v>
+        <v>2845</v>
       </c>
       <c r="C4" t="n">
-        <v>4355</v>
+        <v>4723</v>
       </c>
       <c r="D4" t="n">
-        <v>7159</v>
+        <v>4324</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1450</v>
+        <v>1626</v>
       </c>
       <c r="C5" t="n">
-        <v>3524</v>
+        <v>3061</v>
       </c>
       <c r="D5" t="n">
-        <v>2594</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>802</v>
+        <v>880</v>
       </c>
       <c r="C6" t="n">
-        <v>2534</v>
+        <v>2170</v>
       </c>
       <c r="D6" t="n">
-        <v>1088</v>
+        <v>901</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>318</v>
+        <v>377</v>
       </c>
       <c r="C7" t="n">
-        <v>1377</v>
+        <v>1229</v>
       </c>
       <c r="D7" t="n">
-        <v>609</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="C8" t="n">
-        <v>559</v>
+        <v>510</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6650,7 +6650,7 @@
         <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_69_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_69_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6029</v>
+        <v>1525</v>
       </c>
       <c r="C2" t="n">
-        <v>5381</v>
+        <v>1873</v>
       </c>
       <c r="D2" t="n">
-        <v>19265</v>
+        <v>18059</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3734</v>
+        <v>2848</v>
       </c>
       <c r="C3" t="n">
-        <v>4360</v>
+        <v>4915</v>
       </c>
       <c r="D3" t="n">
-        <v>10998</v>
+        <v>16036</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2923</v>
+        <v>1843</v>
       </c>
       <c r="C4" t="n">
-        <v>4375</v>
+        <v>5498</v>
       </c>
       <c r="D4" t="n">
-        <v>5308</v>
+        <v>6807</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1932</v>
+        <v>773</v>
       </c>
       <c r="C5" t="n">
-        <v>3829</v>
+        <v>2937</v>
       </c>
       <c r="D5" t="n">
-        <v>2098</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1132</v>
+        <v>311</v>
       </c>
       <c r="C6" t="n">
-        <v>2599</v>
+        <v>1060</v>
       </c>
       <c r="D6" t="n">
-        <v>1029</v>
+        <v>762</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>547</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>1698</v>
+        <v>480</v>
       </c>
       <c r="D7" t="n">
-        <v>639</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>213</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>850</v>
+        <v>333</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>370</v>
+        <v>293</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9720</v>
+        <v>1173</v>
       </c>
       <c r="C2" t="n">
-        <v>15284</v>
+        <v>5290</v>
       </c>
       <c r="D2" t="n">
-        <v>21431</v>
+        <v>14561</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3887</v>
+        <v>1859</v>
       </c>
       <c r="C3" t="n">
-        <v>4247</v>
+        <v>2833</v>
       </c>
       <c r="D3" t="n">
-        <v>11431</v>
+        <v>15205</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2812</v>
+        <v>2028</v>
       </c>
       <c r="C4" t="n">
-        <v>4276</v>
+        <v>5106</v>
       </c>
       <c r="D4" t="n">
-        <v>6129</v>
+        <v>8372</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2099</v>
+        <v>1120</v>
       </c>
       <c r="C5" t="n">
-        <v>3974</v>
+        <v>4252</v>
       </c>
       <c r="D5" t="n">
-        <v>2537</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1369</v>
+        <v>478</v>
       </c>
       <c r="C6" t="n">
-        <v>3151</v>
+        <v>2031</v>
       </c>
       <c r="D6" t="n">
-        <v>1189</v>
+        <v>974</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>721</v>
+        <v>173</v>
       </c>
       <c r="C7" t="n">
-        <v>2095</v>
+        <v>774</v>
       </c>
       <c r="D7" t="n">
-        <v>693</v>
+        <v>542</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>318</v>
+        <v>81</v>
       </c>
       <c r="C8" t="n">
-        <v>1231</v>
+        <v>408</v>
       </c>
       <c r="D8" t="n">
-        <v>459</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>573</v>
+        <v>313</v>
       </c>
       <c r="D9" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>280</v>
+        <v>251</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9053</v>
+        <v>609</v>
       </c>
       <c r="C2" t="n">
-        <v>11692</v>
+        <v>2114</v>
       </c>
       <c r="D2" t="n">
-        <v>36396</v>
+        <v>9795</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5097</v>
+        <v>1589</v>
       </c>
       <c r="C3" t="n">
-        <v>7989</v>
+        <v>3708</v>
       </c>
       <c r="D3" t="n">
-        <v>11961</v>
+        <v>14708</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2810</v>
+        <v>2195</v>
       </c>
       <c r="C4" t="n">
-        <v>4173</v>
+        <v>4551</v>
       </c>
       <c r="D4" t="n">
-        <v>6698</v>
+        <v>9306</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2132</v>
+        <v>1116</v>
       </c>
       <c r="C5" t="n">
-        <v>3986</v>
+        <v>5029</v>
       </c>
       <c r="D5" t="n">
-        <v>3011</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1527</v>
+        <v>381</v>
       </c>
       <c r="C6" t="n">
-        <v>3476</v>
+        <v>2751</v>
       </c>
       <c r="D6" t="n">
-        <v>1355</v>
+        <v>995</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>888</v>
+        <v>78</v>
       </c>
       <c r="C7" t="n">
-        <v>2518</v>
+        <v>816</v>
       </c>
       <c r="D7" t="n">
-        <v>758</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>430</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1586</v>
+        <v>458</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>169</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>825</v>
+        <v>245</v>
       </c>
       <c r="D9" t="n">
-        <v>338</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>389</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>220</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>211</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8296</v>
+        <v>1079</v>
       </c>
       <c r="C2" t="n">
-        <v>7763</v>
+        <v>2800</v>
       </c>
       <c r="D2" t="n">
-        <v>29284</v>
+        <v>9199</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5694</v>
+        <v>964</v>
       </c>
       <c r="C3" t="n">
-        <v>10902</v>
+        <v>2492</v>
       </c>
       <c r="D3" t="n">
-        <v>13307</v>
+        <v>13004</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1969</v>
+        <v>1707</v>
       </c>
       <c r="C4" t="n">
-        <v>6190</v>
+        <v>4030</v>
       </c>
       <c r="D4" t="n">
-        <v>6489</v>
+        <v>10008</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1410</v>
+        <v>1424</v>
       </c>
       <c r="C5" t="n">
-        <v>3406</v>
+        <v>4768</v>
       </c>
       <c r="D5" t="n">
-        <v>2166</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>820</v>
+        <v>627</v>
       </c>
       <c r="C6" t="n">
-        <v>2467</v>
+        <v>3864</v>
       </c>
       <c r="D6" t="n">
-        <v>742</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>397</v>
+        <v>168</v>
       </c>
       <c r="C7" t="n">
-        <v>1554</v>
+        <v>1741</v>
       </c>
       <c r="D7" t="n">
-        <v>471</v>
+        <v>624</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>156</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>808</v>
+        <v>625</v>
       </c>
       <c r="D8" t="n">
-        <v>331</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>381</v>
+        <v>333</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4952</v>
+        <v>608</v>
       </c>
       <c r="C2" t="n">
-        <v>3251</v>
+        <v>2715</v>
       </c>
       <c r="D2" t="n">
-        <v>19653</v>
+        <v>6368</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5874</v>
+        <v>880</v>
       </c>
       <c r="C3" t="n">
-        <v>8524</v>
+        <v>2357</v>
       </c>
       <c r="D3" t="n">
-        <v>14947</v>
+        <v>11686</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2939</v>
+        <v>1330</v>
       </c>
       <c r="C4" t="n">
-        <v>8560</v>
+        <v>3333</v>
       </c>
       <c r="D4" t="n">
-        <v>7463</v>
+        <v>10384</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1543</v>
+        <v>1488</v>
       </c>
       <c r="C5" t="n">
-        <v>4674</v>
+        <v>4526</v>
       </c>
       <c r="D5" t="n">
-        <v>2681</v>
+        <v>4924</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>989</v>
+        <v>805</v>
       </c>
       <c r="C6" t="n">
-        <v>2926</v>
+        <v>4368</v>
       </c>
       <c r="D6" t="n">
-        <v>891</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>377</v>
+        <v>203</v>
       </c>
       <c r="C7" t="n">
-        <v>1949</v>
+        <v>2546</v>
       </c>
       <c r="D7" t="n">
-        <v>510</v>
+        <v>694</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>1048</v>
+        <v>948</v>
       </c>
       <c r="D8" t="n">
-        <v>346</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
+        <v>235</v>
+      </c>
+      <c r="D10" t="n">
         <v>234</v>
-      </c>
-      <c r="D10" t="n">
-        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4732</v>
+        <v>1444</v>
       </c>
       <c r="C2" t="n">
-        <v>5661</v>
+        <v>3682</v>
       </c>
       <c r="D2" t="n">
-        <v>18400</v>
+        <v>18541</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4595</v>
+        <v>638</v>
       </c>
       <c r="C3" t="n">
-        <v>5224</v>
+        <v>2213</v>
       </c>
       <c r="D3" t="n">
-        <v>14596</v>
+        <v>10116</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3654</v>
+        <v>998</v>
       </c>
       <c r="C4" t="n">
-        <v>8445</v>
+        <v>2789</v>
       </c>
       <c r="D4" t="n">
-        <v>8529</v>
+        <v>10293</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1899</v>
+        <v>1317</v>
       </c>
       <c r="C5" t="n">
-        <v>6442</v>
+        <v>3847</v>
       </c>
       <c r="D5" t="n">
-        <v>3379</v>
+        <v>5665</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1130</v>
+        <v>1005</v>
       </c>
       <c r="C6" t="n">
-        <v>3730</v>
+        <v>4397</v>
       </c>
       <c r="D6" t="n">
-        <v>1154</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>554</v>
+        <v>387</v>
       </c>
       <c r="C7" t="n">
-        <v>2379</v>
+        <v>3409</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>837</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>193</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>1437</v>
+        <v>1645</v>
       </c>
       <c r="D8" t="n">
-        <v>368</v>
+        <v>519</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="C9" t="n">
-        <v>691</v>
+        <v>642</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D10" t="n">
-        <v>217</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>171</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2806</v>
+        <v>935</v>
       </c>
       <c r="C2" t="n">
-        <v>2595</v>
+        <v>1826</v>
       </c>
       <c r="D2" t="n">
-        <v>12697</v>
+        <v>13202</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4463</v>
+        <v>1018</v>
       </c>
       <c r="C3" t="n">
-        <v>5157</v>
+        <v>2818</v>
       </c>
       <c r="D3" t="n">
-        <v>14671</v>
+        <v>11543</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4033</v>
+        <v>1690</v>
       </c>
       <c r="C4" t="n">
-        <v>8047</v>
+        <v>3951</v>
       </c>
       <c r="D4" t="n">
-        <v>9261</v>
+        <v>10876</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1995</v>
+        <v>1050</v>
       </c>
       <c r="C5" t="n">
-        <v>7762</v>
+        <v>5903</v>
       </c>
       <c r="D5" t="n">
-        <v>3684</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>981</v>
+        <v>357</v>
       </c>
       <c r="C6" t="n">
-        <v>4664</v>
+        <v>4590</v>
       </c>
       <c r="D6" t="n">
-        <v>1149</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>178</v>
+        <v>87</v>
       </c>
       <c r="C7" t="n">
-        <v>2566</v>
+        <v>1612</v>
       </c>
       <c r="D7" t="n">
-        <v>572</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>1127</v>
+        <v>629</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>167</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3340</v>
+        <v>526</v>
       </c>
       <c r="C2" t="n">
-        <v>3144</v>
+        <v>1135</v>
       </c>
       <c r="D2" t="n">
-        <v>11952</v>
+        <v>9113</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3224</v>
+        <v>832</v>
       </c>
       <c r="C3" t="n">
-        <v>3505</v>
+        <v>2018</v>
       </c>
       <c r="D3" t="n">
-        <v>13416</v>
+        <v>10950</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3685</v>
+        <v>1142</v>
       </c>
       <c r="C4" t="n">
-        <v>6541</v>
+        <v>3174</v>
       </c>
       <c r="D4" t="n">
-        <v>9862</v>
+        <v>10240</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2506</v>
+        <v>963</v>
       </c>
       <c r="C5" t="n">
-        <v>7806</v>
+        <v>4340</v>
       </c>
       <c r="D5" t="n">
-        <v>4428</v>
+        <v>5510</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1260</v>
+        <v>374</v>
       </c>
       <c r="C6" t="n">
-        <v>6004</v>
+        <v>4325</v>
       </c>
       <c r="D6" t="n">
-        <v>1510</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>382</v>
+        <v>82</v>
       </c>
       <c r="C7" t="n">
-        <v>3478</v>
+        <v>2165</v>
       </c>
       <c r="D7" t="n">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>1684</v>
+        <v>686</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>588</v>
+        <v>276</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>141</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2525</v>
+        <v>579</v>
       </c>
       <c r="C2" t="n">
-        <v>2395</v>
+        <v>2317</v>
       </c>
       <c r="D2" t="n">
-        <v>8938</v>
+        <v>14883</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2857</v>
+        <v>569</v>
       </c>
       <c r="C3" t="n">
-        <v>3041</v>
+        <v>1318</v>
       </c>
       <c r="D3" t="n">
-        <v>12510</v>
+        <v>9835</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3237</v>
+        <v>860</v>
       </c>
       <c r="C4" t="n">
-        <v>5310</v>
+        <v>2431</v>
       </c>
       <c r="D4" t="n">
-        <v>10134</v>
+        <v>10071</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2744</v>
+        <v>956</v>
       </c>
       <c r="C5" t="n">
-        <v>7469</v>
+        <v>3630</v>
       </c>
       <c r="D5" t="n">
-        <v>5004</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1501</v>
+        <v>600</v>
       </c>
       <c r="C6" t="n">
-        <v>6827</v>
+        <v>4282</v>
       </c>
       <c r="D6" t="n">
-        <v>1773</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>359</v>
+        <v>192</v>
       </c>
       <c r="C7" t="n">
-        <v>4358</v>
+        <v>3328</v>
       </c>
       <c r="D7" t="n">
-        <v>710</v>
+        <v>866</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C8" t="n">
-        <v>2153</v>
+        <v>1431</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>699</v>
+        <v>471</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>203</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4918</v>
+        <v>1489</v>
       </c>
       <c r="C2" t="n">
-        <v>9690</v>
+        <v>6799</v>
       </c>
       <c r="D2" t="n">
-        <v>11781</v>
+        <v>20863</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2301</v>
+        <v>479</v>
       </c>
       <c r="C3" t="n">
-        <v>2487</v>
+        <v>1600</v>
       </c>
       <c r="D3" t="n">
-        <v>11352</v>
+        <v>9909</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2693</v>
+        <v>623</v>
       </c>
       <c r="C4" t="n">
-        <v>4168</v>
+        <v>1771</v>
       </c>
       <c r="D4" t="n">
-        <v>10070</v>
+        <v>9625</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2689</v>
+        <v>831</v>
       </c>
       <c r="C5" t="n">
-        <v>6473</v>
+        <v>2921</v>
       </c>
       <c r="D5" t="n">
-        <v>5590</v>
+        <v>6756</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1796</v>
+        <v>710</v>
       </c>
       <c r="C6" t="n">
-        <v>7020</v>
+        <v>3903</v>
       </c>
       <c r="D6" t="n">
-        <v>2184</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>647</v>
+        <v>339</v>
       </c>
       <c r="C7" t="n">
-        <v>5299</v>
+        <v>3803</v>
       </c>
       <c r="D7" t="n">
-        <v>838</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="8">
@@ -3663,10 +3663,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>2972</v>
+        <v>2341</v>
       </c>
       <c r="D8" t="n">
         <v>458</v>
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>1183</v>
+        <v>912</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>385</v>
+        <v>321</v>
       </c>
       <c r="D10" t="n">
-        <v>192</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6724</v>
+        <v>4285</v>
       </c>
       <c r="C2" t="n">
-        <v>5972</v>
+        <v>4144</v>
       </c>
       <c r="D2" t="n">
-        <v>7478</v>
+        <v>10276</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3480</v>
+        <v>1903</v>
       </c>
       <c r="C2" t="n">
-        <v>5426</v>
+        <v>9628</v>
       </c>
       <c r="D2" t="n">
-        <v>8670</v>
+        <v>20445</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3281</v>
+        <v>752</v>
       </c>
       <c r="C3" t="n">
-        <v>4426</v>
+        <v>3604</v>
       </c>
       <c r="D3" t="n">
-        <v>12328</v>
+        <v>10804</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3830</v>
+        <v>487</v>
       </c>
       <c r="C4" t="n">
-        <v>6214</v>
+        <v>1647</v>
       </c>
       <c r="D4" t="n">
-        <v>10278</v>
+        <v>9381</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1758</v>
+        <v>675</v>
       </c>
       <c r="C5" t="n">
-        <v>9722</v>
+        <v>2297</v>
       </c>
       <c r="D5" t="n">
-        <v>5148</v>
+        <v>6953</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>597</v>
+        <v>715</v>
       </c>
       <c r="C6" t="n">
-        <v>6637</v>
+        <v>3401</v>
       </c>
       <c r="D6" t="n">
-        <v>1784</v>
+        <v>3723</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>122</v>
+        <v>453</v>
       </c>
       <c r="C7" t="n">
-        <v>2912</v>
+        <v>3810</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>170</v>
       </c>
       <c r="C8" t="n">
-        <v>1159</v>
+        <v>2999</v>
       </c>
       <c r="D8" t="n">
-        <v>303</v>
+        <v>548</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>377</v>
+        <v>1527</v>
       </c>
       <c r="D9" t="n">
-        <v>188</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>161</v>
+        <v>564</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>214</v>
       </c>
       <c r="D11" t="n">
-        <v>95</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7517</v>
+        <v>5314</v>
       </c>
       <c r="C2" t="n">
-        <v>6736</v>
+        <v>4720</v>
       </c>
       <c r="D2" t="n">
-        <v>9378</v>
+        <v>19215</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2856</v>
+        <v>1416</v>
       </c>
       <c r="C3" t="n">
-        <v>3009</v>
+        <v>1636</v>
       </c>
       <c r="D3" t="n">
-        <v>1895</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4753</v>
+        <v>3467</v>
       </c>
       <c r="C2" t="n">
-        <v>4994</v>
+        <v>3977</v>
       </c>
       <c r="D2" t="n">
-        <v>16829</v>
+        <v>24851</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4259</v>
+        <v>2850</v>
       </c>
       <c r="C3" t="n">
-        <v>4438</v>
+        <v>3004</v>
       </c>
       <c r="D3" t="n">
-        <v>3012</v>
+        <v>4894</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1274</v>
+        <v>680</v>
       </c>
       <c r="C4" t="n">
-        <v>1834</v>
+        <v>1068</v>
       </c>
       <c r="D4" t="n">
-        <v>1563</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5070</v>
+        <v>3427</v>
       </c>
       <c r="C2" t="n">
-        <v>4312</v>
+        <v>4604</v>
       </c>
       <c r="D2" t="n">
-        <v>13848</v>
+        <v>21955</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3713</v>
+        <v>2607</v>
       </c>
       <c r="C3" t="n">
-        <v>4103</v>
+        <v>3071</v>
       </c>
       <c r="D3" t="n">
-        <v>5005</v>
+        <v>7886</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2342</v>
+        <v>1546</v>
       </c>
       <c r="C4" t="n">
-        <v>3270</v>
+        <v>2216</v>
       </c>
       <c r="D4" t="n">
-        <v>1793</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>583</v>
+        <v>341</v>
       </c>
       <c r="C5" t="n">
-        <v>1096</v>
+        <v>706</v>
       </c>
       <c r="D5" t="n">
-        <v>1207</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5876</v>
+        <v>3188</v>
       </c>
       <c r="C2" t="n">
-        <v>5900</v>
+        <v>4318</v>
       </c>
       <c r="D2" t="n">
-        <v>15224</v>
+        <v>25619</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3582</v>
+        <v>2481</v>
       </c>
       <c r="C3" t="n">
-        <v>3659</v>
+        <v>3426</v>
       </c>
       <c r="D3" t="n">
-        <v>5996</v>
+        <v>9569</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2564</v>
+        <v>1782</v>
       </c>
       <c r="C4" t="n">
-        <v>3657</v>
+        <v>2641</v>
       </c>
       <c r="D4" t="n">
-        <v>2307</v>
+        <v>3158</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1219</v>
+        <v>812</v>
       </c>
       <c r="C5" t="n">
-        <v>2221</v>
+        <v>1546</v>
       </c>
       <c r="D5" t="n">
-        <v>1277</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>314</v>
+        <v>204</v>
       </c>
       <c r="C6" t="n">
-        <v>703</v>
+        <v>500</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>843</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>292</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>251</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6770</v>
+        <v>4089</v>
       </c>
       <c r="C2" t="n">
-        <v>8689</v>
+        <v>5461</v>
       </c>
       <c r="D2" t="n">
-        <v>25177</v>
+        <v>31714</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3432</v>
+        <v>2323</v>
       </c>
       <c r="C3" t="n">
-        <v>3951</v>
+        <v>3384</v>
       </c>
       <c r="D3" t="n">
-        <v>6563</v>
+        <v>11448</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1920</v>
+        <v>1834</v>
       </c>
       <c r="C4" t="n">
-        <v>3000</v>
+        <v>3023</v>
       </c>
       <c r="D4" t="n">
-        <v>2518</v>
+        <v>4292</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>989</v>
+        <v>1111</v>
       </c>
       <c r="C5" t="n">
-        <v>2162</v>
+        <v>2102</v>
       </c>
       <c r="D5" t="n">
-        <v>1156</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>364</v>
+        <v>445</v>
       </c>
       <c r="C6" t="n">
-        <v>999</v>
+        <v>1036</v>
       </c>
       <c r="D6" t="n">
-        <v>757</v>
+        <v>896</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="C7" t="n">
-        <v>337</v>
+        <v>397</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>276</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5382</v>
+        <v>3414</v>
       </c>
       <c r="C2" t="n">
-        <v>4225</v>
+        <v>7900</v>
       </c>
       <c r="D2" t="n">
-        <v>20417</v>
+        <v>33572</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4269</v>
+        <v>2593</v>
       </c>
       <c r="C3" t="n">
-        <v>5814</v>
+        <v>3864</v>
       </c>
       <c r="D3" t="n">
-        <v>9345</v>
+        <v>13722</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2364</v>
+        <v>1765</v>
       </c>
       <c r="C4" t="n">
-        <v>3493</v>
+        <v>3150</v>
       </c>
       <c r="D4" t="n">
-        <v>3295</v>
+        <v>5466</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1307</v>
+        <v>1282</v>
       </c>
       <c r="C5" t="n">
-        <v>2623</v>
+        <v>2526</v>
       </c>
       <c r="D5" t="n">
-        <v>1395</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>628</v>
+        <v>673</v>
       </c>
       <c r="C6" t="n">
-        <v>1667</v>
+        <v>1546</v>
       </c>
       <c r="D6" t="n">
-        <v>815</v>
+        <v>985</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="C7" t="n">
-        <v>719</v>
+        <v>699</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>661</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="C8" t="n">
-        <v>286</v>
+        <v>346</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5162</v>
+        <v>3106</v>
       </c>
       <c r="C2" t="n">
-        <v>5717</v>
+        <v>4740</v>
       </c>
       <c r="D2" t="n">
-        <v>18934</v>
+        <v>26183</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3971</v>
+        <v>3337</v>
       </c>
       <c r="C3" t="n">
-        <v>4260</v>
+        <v>6287</v>
       </c>
       <c r="D3" t="n">
-        <v>10443</v>
+        <v>15316</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2845</v>
+        <v>1184</v>
       </c>
       <c r="C4" t="n">
-        <v>4723</v>
+        <v>4451</v>
       </c>
       <c r="D4" t="n">
-        <v>4324</v>
+        <v>5099</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1626</v>
+        <v>621</v>
       </c>
       <c r="C5" t="n">
-        <v>3061</v>
+        <v>1515</v>
       </c>
       <c r="D5" t="n">
-        <v>1717</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>880</v>
+        <v>226</v>
       </c>
       <c r="C6" t="n">
-        <v>2170</v>
+        <v>685</v>
       </c>
       <c r="D6" t="n">
-        <v>901</v>
+        <v>647</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>377</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>1229</v>
+        <v>339</v>
       </c>
       <c r="D7" t="n">
-        <v>602</v>
+        <v>460</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>510</v>
+        <v>281</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
